--- a/sheets/Libetee_6500万作戦.xlsx
+++ b/sheets/Libetee_6500万作戦.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="サマリー" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="達成早見表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="転換率を守る7策" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="客単価を上げる7策" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="グラフ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="決定施策_6本柱" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="達成早見表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="転換率を守る7策" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="客単価を上げる7策" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="グラフ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -108,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +154,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -759,29 +769,48 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>読み方：転換率の下落を−8.3%以内に抑えれば(保持91.7%)、アクセス増だけで65M。</t>
-        </is>
-      </c>
-    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>【決定版】×0.9回復＋セット率5%（6本柱）</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>66262794</v>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>1262794</v>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>達成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>推奨は併用：転換率防衛7策で「下落−12%以内」＋ セット販売でお客様の5%が2個購入 → ¥65.0M。</t>
+          <t>読み方：転換率の下落を−8.3%以内に抑えれば(保持91.7%)、アクセス増だけで65M。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>セット1組の追加売上＝2個目¥29,500−クーポン¥5,000＝¥24,500。必要セット数：5%＝約91組/月。</t>
+          <t>推奨は併用：転換率防衛7策で「下落−12%以内」＋ セット販売でお客様の5%が2個購入 → ¥65.0M。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>セット1組の追加売上＝2個目¥29,500−クーポン¥5,000＝¥24,500。必要セット数：5%＝約91組/月。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>前提：スーツケース在庫（マットブラックS筆頭・かぶり日8/5・10・25の3日分）。</t>
         </is>
@@ -797,6 +826,228 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>決定施策（社長決定・6本柱）→ 月商¥66.3M（目標65M達成・+¥1.26M上振れ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>段階</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>施策</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>狙い・効果</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>数字への効き方</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>認知</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>インフルエンサー広告を積極運用</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>平日に種まき。UGC/レビュー型の信頼素材にもなり、メタのクリエイティブへ転用</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>転換率の防衛に寄与</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>認知</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>テレビ出演を後ろ盾にメタで認知拡大</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>放映実績を広告1枚目・LP冒頭に。放映が決まれば当日に広告増額をぶつける</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>転換率の防衛に寄与</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>流入・刈り取り</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>イベント日に刈り取り</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>かぶり日8/5・10・25に広告最厚（平日の8倍返し）。5と0・マラソンで回収</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>攻めプランの土台</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>転換率</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>スーツケースのコンテンツページ新設</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>動画LP化（フロントオープン/ストッパー/静音キャスター実演）で転換率×0.8→×0.9へ回復</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>+¥6.1M（57.9→64.0M）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>客単価</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>セット購入で¥5,000引き</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>目標セット率5%＝約91組/月。2個目の獲得コスト¥5,000＜広告CPA(平日約¥6,600)</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>+¥2.3M（→66.3M）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>リピート</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>リピーター限定¥2,000オフ</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>限定表示（他の人には見えない）で値崩れなしに再購入喚起。9月スーパーSALE(×2.4)の土台</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>9月以降のLTV資産</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>数字の積み上げ：攻め(×0.8)¥57.9M → ＋④で¥64.0M → ＋⑤で¥66.3M（目標65Mに+¥1.26M上振れ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>前提：スーツケース在庫（マットブラックS・かぶり日3日分）。KPI：転換率(週次)・セット率・アプリ経由比率。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1024,198 +1275,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>転換率を「据え置き」に守る7策</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>施策</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>中身</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>楽天アプリへ流す導線</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>7月実測：アプリ転換率4〜8% vs スマホWeb0.03〜0.13%（約50倍）。メタ→アプリで開かせる（ディープリンク/アプリ限定クーポン訴求）。増えた流入の質が別物になる</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>S 最優先</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>テレビ出演・放映実績の活用</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>ヒルナンデス実績を広告1枚目・LPファーストビューへ。新規TV露出が決まれば放映日に広告増額をぶつける</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>LPに動きをつける（動画LP化）</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>ファーストビュー6秒動画：フロントオープン→ストッパー→静音キャスター実演。GIF/ショート動画は冷たい流入に強い</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>楽天広告(RPP/CA)の精度</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>検索語の絞込・除外、売れ筋SKU(多機能PC)へ入札集中、イベント日だけ増額の山谷運用</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>メタ広告の精度</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>購入者リストの類似オーディエンス、動画視聴→カート→購入のリタゲ階層、レビュー/UGC型クリエイティブ</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>商品ページCRO</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>レビュー動画・サイズ比較表・Q&amp;A先回り・クーポン視認性UP</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>カゴ落ち回収</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>カート放棄への再訪クーポン(Rクーポン)。最も安い転換率改善</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1239,7 +1298,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>客単価を上げる7策</t>
+          <t>転換率を「据え置き」に守る7策</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1330,12 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>2個セット¥5,000クーポン【社長案】</t>
+          <t>楽天アプリへ流す導線</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>2個目の獲得コスト¥5,000＜広告の新規獲得(平日約¥6,600)。対象：多機能PC/ノーマルアルミ/多機能アルミ。目標セット率5%＝約91組/月</t>
+          <t>7月実測：アプリ転換率4〜8% vs スマホWeb0.03〜0.13%（約50倍）。メタ→アプリで開かせる（ディープリンク/アプリ限定クーポン訴求）。増えた流入の質が別物になる</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
@@ -1291,12 +1350,12 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>S→Mアップセル</t>
+          <t>テレビ出演・放映実績の活用</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>購入者の57%がSサイズ。「+¥6,900でMサイズ(3〜7泊)」比較表を目立たせる。値引きゼロで客単価UP</t>
+          <t>ヒルナンデス実績を広告1枚目・LPファーストビューへ。新規TV露出が決まれば放映日に広告増額をぶつける</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -1311,12 +1370,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>圧縮バッグ同梱の拡販</t>
+          <t>LPに動きをつける（動画LP化）</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>SCセット1000円OFFは既に月17組の実績。全SCページに同梱枠を設置</t>
+          <t>ファーストビュー6秒動画：フロントオープン→ストッパー→静音キャスター実演。GIF/ショート動画は冷たい流入に強い</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -1331,12 +1390,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>段階クーポン（3個¥9,000）</t>
+          <t>楽天広告(RPP/CA)の精度</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>家族・帰省需要。8月は「家族分まとめて」が刺さる季節</t>
+          <t>検索語の絞込・除外、売れ筋SKU(多機能PC)へ入札集中、イベント日だけ増額の山谷運用</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -1351,17 +1410,17 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>ペア割の見せ方</t>
+          <t>メタ広告の精度</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>同じ2個割でも「夫婦で色違い」訴求（マットブラック×シルバー提案）</t>
+          <t>購入者リストの類似オーディエンス、動画視聴→カート→購入のリタゲ階層、レビュー/UGC型クリエイティブ</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1430,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>夏旅セット（SC＋ハンディファン）</t>
+          <t>商品ページCRO</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>旅行文脈のクロスセル。ファン在庫消化にも効く</t>
+          <t>レビュー動画・サイズ比較表・Q&amp;A先回り・クーポン視認性UP</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -1391,12 +1450,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>お盆・帰省ギフト訴求</t>
+          <t>カゴ落ち回収</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>のし・ラッピング対応を前面に。8月特有の贈答・買い替え需要</t>
+          <t>カート放棄への再訪クーポン(Rクーポン)。最も安い転換率改善</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -1419,6 +1478,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>客単価を上げる7策</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>施策</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>中身</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>2個セット¥5,000クーポン【社長案】</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2個目の獲得コスト¥5,000＜広告の新規獲得(平日約¥6,600)。対象：多機能PC/ノーマルアルミ/多機能アルミ。目標セット率5%＝約91組/月</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>S 最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>S→Mアップセル</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>購入者の57%がSサイズ。「+¥6,900でMサイズ(3〜7泊)」比較表を目立たせる。値引きゼロで客単価UP</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>圧縮バッグ同梱の拡販</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>SCセット1000円OFFは既に月17組の実績。全SCページに同梱枠を設置</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>段階クーポン（3個¥9,000）</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>家族・帰省需要。8月は「家族分まとめて」が刺さる季節</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ペア割の見せ方</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>同じ2個割でも「夫婦で色違い」訴求（マットブラック×シルバー提案）</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>夏旅セット（SC＋ハンディファン）</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>旅行文脈のクロスセル。ファン在庫消化にも効く</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>お盆・帰省ギフト訴求</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>のし・ラッピング対応を前面に。8月特有の贈答・買い替え需要</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
